--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.15884795983821</v>
+        <v>5.713312793473708</v>
       </c>
       <c r="D2" t="n">
-        <v>16.56079801411144</v>
+        <v>2.69112967729311</v>
       </c>
       <c r="E2" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F2" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.27131008438726</v>
+        <v>7.51908788871293</v>
       </c>
       <c r="D3" t="n">
-        <v>46.63243154480129</v>
+        <v>7.57777012603021</v>
       </c>
       <c r="E3" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F3" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.92696495888363</v>
+        <v>1.61313180581859</v>
       </c>
       <c r="D4" t="n">
-        <v>11.3029356534292</v>
+        <v>1.836727043682245</v>
       </c>
       <c r="E4" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F4" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.05881114661549</v>
+        <v>4.072056811325018</v>
       </c>
       <c r="D5" t="n">
-        <v>25.11062237313848</v>
+        <v>4.080476135635003</v>
       </c>
       <c r="E5" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F5" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.29913193291735</v>
+        <v>7.361108939099069</v>
       </c>
       <c r="D6" t="n">
-        <v>46.94999972882038</v>
+        <v>7.629374955933312</v>
       </c>
       <c r="E6" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F6" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.267984556461</v>
+        <v>2.156047490424912</v>
       </c>
       <c r="D7" t="n">
-        <v>11.91078650733854</v>
+        <v>1.935502807442513</v>
       </c>
       <c r="E7" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F7" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.30759797878562</v>
+        <v>6.712484671552663</v>
       </c>
       <c r="D8" t="n">
-        <v>41.2596687658104</v>
+        <v>6.704696174444191</v>
       </c>
       <c r="E8" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F8" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.12584121993248</v>
+        <v>4.245449198239029</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40795353639536</v>
+        <v>4.453792449664247</v>
       </c>
       <c r="E9" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F9" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.36632873629424</v>
+        <v>5.259528419647814</v>
       </c>
       <c r="D10" t="n">
-        <v>30.91216244164244</v>
+        <v>5.023226396766897</v>
       </c>
       <c r="E10" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F10" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.67423761492635</v>
+        <v>7.422063612425533</v>
       </c>
       <c r="D11" t="n">
-        <v>44.12445308615967</v>
+        <v>7.170223626500946</v>
       </c>
       <c r="E11" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F11" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.23968059054764</v>
+        <v>2.151448095963991</v>
       </c>
       <c r="D12" t="n">
-        <v>12.15614447557478</v>
+        <v>1.975373477280901</v>
       </c>
       <c r="E12" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F12" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>10.28861218344099</v>
+        <v>1.671899479809161</v>
       </c>
       <c r="D13" t="n">
-        <v>10.05151085343676</v>
+        <v>1.633370513683474</v>
       </c>
       <c r="E13" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F13" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.34543275919408</v>
+        <v>1.843632823369038</v>
       </c>
       <c r="D14" t="n">
-        <v>10.74265194597165</v>
+        <v>1.745680941220393</v>
       </c>
       <c r="E14" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F14" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.59207509751824</v>
+        <v>3.671212203346714</v>
       </c>
       <c r="D15" t="n">
-        <v>22.28672962667035</v>
+        <v>3.621593564333933</v>
       </c>
       <c r="E15" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F15" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.1048855210632</v>
+        <v>6.67954389717277</v>
       </c>
       <c r="D16" t="n">
-        <v>39.45910399898343</v>
+        <v>6.412104399834807</v>
       </c>
       <c r="E16" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F16" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.80901854589579</v>
+        <v>5.331465513708066</v>
       </c>
       <c r="D17" t="n">
-        <v>32.63919304992545</v>
+        <v>5.303868870612885</v>
       </c>
       <c r="E17" t="n">
-        <v>13.18341911418115</v>
+        <v>2.142305606054437</v>
       </c>
       <c r="F17" t="n">
-        <v>13.37644668419214</v>
+        <v>2.173672586181223</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
